--- a/InputData/trans/FoVBPD/Fraction of Vehicle Batteries Produced Domestically.xlsx
+++ b/InputData/trans/FoVBPD/Fraction of Vehicle Batteries Produced Domestically.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\FoVBPD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onewri-my.sharepoint.com/personal/varun_agarwal_wri_org/Documents/EPS India 2.0/EPS 2023/EPS India Update-2023-24/Completed EPS Variables/trans/FoVBPD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AECF23-A61B-44F8-B5D9-89EF6743C0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{B9AECF23-A61B-44F8-B5D9-89EF6743C0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFA69648-4599-4F51-9F3A-FD8D0E936418}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="FoVBPD" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -34,12 +37,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>FoVBPD Fraction of Vehicle Batteries Produced Domestically</t>
+  </si>
   <si>
     <t>Sources:</t>
   </si>
   <si>
-    <t>FoVBPD Fraction of Vehicle Batteries Produced Domestically</t>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>This variable affects what portion of newly sold vehicles qualify for Vehicle Battery Production subsidy,</t>
   </si>
   <si>
     <t>Dmnl</t>
@@ -48,38 +57,23 @@
     <t>Fraction of Vehicle Batteries Produced Domestically</t>
   </si>
   <si>
-    <t>ICCT and Energy Innovation</t>
+    <t>if relevant.</t>
   </si>
   <si>
-    <t>Analyzing the Impact of the Inflation Reduction Act on Electric Vehicle Uptake in the United States</t>
+    <t>Department of Heavy Industries</t>
   </si>
   <si>
-    <t>https://energyinnovation.org/wp-content/uploads/2023/01/IRA-EV-assessment-white-paper-letter-v46.pdf</t>
+    <t>Production Linked Incentive (PLI) scheme - National Programme on Advanced Chemistry Cell (ACC) Battery Storage</t>
   </si>
   <si>
-    <t>Table 1</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>This variable affects what portion of newly sold vehicles qualify for Vehicle Battery Production subsidy,</t>
-  </si>
-  <si>
-    <t>if relevant. We assume that the U.S. has enough battery manufacturing capacity to supply</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100% of vehicle battery demand domestically. All U.S. state models should use the U.S. vaues, since the </t>
-  </si>
-  <si>
-    <t>battery manufacturing production tax credit applies to all U.S. manufactured batteries.</t>
+    <t>https://heavyindustries.gov.in/sites/default/files/2023-09/ACC%20Scheme%20Notification%209June21.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,6 +85,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -113,10 +115,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -125,8 +128,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -142,10 +147,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -183,7 +192,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -289,7 +298,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -431,7 +440,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -439,74 +448,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF982137-6F01-4109-8226-D4C6F3731BA9}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="101.28515625" customWidth="1"/>
+    <col min="2" max="2" width="101.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="2">
-        <v>2023</v>
+        <v>2021</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>6</v>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B6" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{0F016A46-B529-4ECB-8DC6-C9DBB76426F3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -516,15 +513,15 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.5703125" customWidth="1"/>
+    <col min="1" max="1" width="31.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -616,43 +613,103 @@
       <c r="AE1">
         <v>2050</v>
       </c>
+      <c r="AF1">
+        <v>2051</v>
+      </c>
+      <c r="AG1">
+        <v>2052</v>
+      </c>
+      <c r="AH1">
+        <v>2053</v>
+      </c>
+      <c r="AI1">
+        <v>2054</v>
+      </c>
+      <c r="AJ1">
+        <v>2055</v>
+      </c>
+      <c r="AK1">
+        <v>2056</v>
+      </c>
+      <c r="AL1">
+        <v>2057</v>
+      </c>
+      <c r="AM1">
+        <v>2058</v>
+      </c>
+      <c r="AN1">
+        <v>2059</v>
+      </c>
+      <c r="AO1">
+        <v>2060</v>
+      </c>
+      <c r="AP1">
+        <v>2061</v>
+      </c>
+      <c r="AQ1">
+        <v>2062</v>
+      </c>
+      <c r="AR1">
+        <v>2063</v>
+      </c>
+      <c r="AS1">
+        <v>2064</v>
+      </c>
+      <c r="AT1">
+        <v>2065</v>
+      </c>
+      <c r="AU1">
+        <v>2066</v>
+      </c>
+      <c r="AV1">
+        <v>2067</v>
+      </c>
+      <c r="AW1">
+        <v>2068</v>
+      </c>
+      <c r="AX1">
+        <v>2069</v>
+      </c>
+      <c r="AY1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:31" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3">
-        <v>1</v>
+        <v>6.25E-2</v>
       </c>
       <c r="D2" s="3">
-        <v>1</v>
+        <v>0.125</v>
       </c>
       <c r="E2" s="3">
-        <v>1</v>
+        <v>0.1875</v>
       </c>
       <c r="F2" s="3">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="G2" s="3">
-        <v>1</v>
+        <v>0.33750000000000002</v>
       </c>
       <c r="H2" s="3">
-        <v>1</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="I2" s="3">
-        <v>1</v>
+        <v>0.51249999999999996</v>
       </c>
       <c r="J2" s="3">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K2" s="3">
-        <v>1</v>
+        <v>0.71479999999999999</v>
       </c>
       <c r="L2" s="3">
-        <v>1</v>
+        <v>0.85160000000000002</v>
       </c>
       <c r="M2" s="3">
         <v>1</v>
@@ -709,10 +766,245 @@
         <v>1</v>
       </c>
       <c r="AE2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AJ2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AL2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AN2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AP2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AQ2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AR2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AS2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AT2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AU2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AV2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AW2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AX2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AY2" s="3">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DDC1145-7972-4920-A10A-C3A70A51FEDA}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83817F45-89B7-4308-AF1E-0F1E7821255F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7FA2164-ECCB-4C55-92C6-F93920C62CCE}"/>
 </file>